--- a/python-excel-portfolio-optimization-demo.xlsx
+++ b/python-excel-portfolio-optimization-demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2000001_{9EA5884A-43DE-4136-ABCF-38CBB1A7A88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB60676-088A-457A-8C8D-0EB2D1AAE7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -298,8 +298,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmm\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -358,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -372,6 +373,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,8 +439,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>524098</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>938965</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>132089</xdr:rowOff>
     </xdr:to>
@@ -657,9 +660,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MonthlyReturns" displayName="MonthlyReturns" ref="A1:G73" headerRowDxfId="8" dataDxfId="6" totalsRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MonthlyReturns" displayName="MonthlyReturns" ref="A1:G73" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="7">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Broad Market ETF" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Growth ETF" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Value ETF" dataDxfId="3"/>
@@ -830,7 +833,11 @@
     <col min="5" max="5" width="7.5546875" style="6" customWidth="1"/>
     <col min="6" max="6" width="12.21875" style="6" customWidth="1"/>
     <col min="7" max="7" width="12.77734375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="15.38671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" customWidth="1"/>
+    <col min="10" max="10" width="15.38671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.94140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.71875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.35">
@@ -947,22 +954,22 @@
       <c r="I3" vm="1">
         <v>43831</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="7">
         <v>9.0283004794234067E-3</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="7">
         <v>-3.0251375707132482E-2</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="7">
         <v>3.6727007535694592E-2</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="7">
         <v>3.1782878554182316E-3</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="7">
         <v>-4.241651381605073E-2</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="7">
         <v>1.2526050360841801E-2</v>
       </c>
     </row>
@@ -991,22 +998,22 @@
       <c r="I4" vm="2">
         <v>43862</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="7">
         <v>-4.3933030359427944E-2</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="7">
         <v>-0.12088491862314756</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="7">
         <v>-7.0715863676535217E-3</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="7">
         <v>4.1249138307288607E-3</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="7">
         <v>-1.0423682595146672E-2</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="7">
         <v>7.5118492622364808E-2</v>
       </c>
     </row>
@@ -1035,22 +1042,22 @@
       <c r="I5" vm="3">
         <v>43891</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="7">
         <v>-0.12547140066468998</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="7">
         <v>-0.16956443590088105</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="7">
         <v>-8.8592467997763144E-2</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="7">
         <v>2.4127936906253415E-2</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="7">
         <v>-0.1135995257562545</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="7">
         <v>-0.16270797546686527</v>
       </c>
     </row>
@@ -1079,22 +1086,22 @@
       <c r="I6" vm="4">
         <v>43922</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="7">
         <v>0.11978188039335548</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="7">
         <v>0.24069301040172053</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="7">
         <v>7.9697264314192939E-2</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="7">
         <v>-8.4645544032112639E-3</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="7">
         <v>1.9493637036092151E-2</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="7">
         <v>-9.8555194063416021E-2</v>
       </c>
     </row>
@@ -1123,22 +1130,22 @@
       <c r="I7" vm="5">
         <v>43952</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="7">
         <v>2.2439646456416308E-2</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="7">
         <v>3.4030429350572974E-2</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="7">
         <v>3.6176904776616045E-2</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="7">
         <v>3.9947575019489432E-4</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="7">
         <v>6.6667325414408202E-2</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="7">
         <v>-1.2397507533625424E-2</v>
       </c>
     </row>
@@ -1191,7 +1198,7 @@
         <f t="array" ref="I9:J13">_xlfn._xlws.PY(1,0)</f>
         <v>Broad Market ETF</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="7">
         <v>-6.4264249187204734E-4</v>
       </c>
     </row>
@@ -1220,7 +1227,7 @@
       <c r="I10" t="str">
         <v>Growth ETF</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="7">
         <v>-1.037801303749E-3</v>
       </c>
     </row>
@@ -1249,7 +1256,7 @@
       <c r="I11" t="str">
         <v>Value ETF</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="7">
         <v>5.0794172176916149E-3</v>
       </c>
     </row>
@@ -1278,7 +1285,7 @@
       <c r="I12" t="str">
         <v>Bond ETF</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="7">
         <v>6.7263284308553646E-3</v>
       </c>
     </row>
@@ -1307,7 +1314,7 @@
       <c r="I13" t="str">
         <v>Real Estate ETF</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="7">
         <v>-3.89766261108001E-3</v>
       </c>
     </row>
@@ -1379,7 +1386,7 @@
       <c r="G16" s="1">
         <v>-2.9183834137412931E-2</v>
       </c>
-      <c r="I16" cm="1">
+      <c r="I16" s="8" cm="1">
         <f t="array" ref="I16:I21">_xlfn._xlws.PY(2,0)</f>
         <v>0.16666666666666666</v>
       </c>
@@ -1406,7 +1413,7 @@
       <c r="G17" s="1">
         <v>6.1592245519824305E-2</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="8">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1432,7 +1439,7 @@
       <c r="G18" s="1">
         <v>2.6919357879505605E-2</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="8">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1458,7 +1465,7 @@
       <c r="G19" s="1">
         <v>-5.5776355852202156E-2</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="8">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1484,7 +1491,7 @@
       <c r="G20" s="1">
         <v>-2.2403220148965883E-2</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="8">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1510,7 +1517,7 @@
       <c r="G21" s="1">
         <v>2.1892009091152381E-2</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="8">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1536,6 +1543,7 @@
       <c r="G22" s="1">
         <v>-2.3519564472677074E-2</v>
       </c>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="5">
@@ -1936,7 +1944,7 @@
       <c r="I37" t="str">
         <v>Broad Market ETF</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="7">
         <v>2.8882970087117231E-2</v>
       </c>
     </row>
@@ -1965,7 +1973,7 @@
       <c r="I38" t="str">
         <v>Growth ETF</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1994,7 +2002,7 @@
       <c r="I39" t="str">
         <v>Value ETF</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="7">
         <v>0.19545778399039818</v>
       </c>
     </row>
@@ -2023,7 +2031,7 @@
       <c r="I40" t="str">
         <v>Bond ETF</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="7">
         <v>0.7756592459224847</v>
       </c>
     </row>
@@ -2052,7 +2060,7 @@
       <c r="I41" t="str">
         <v>Real Estate ETF</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="7">
         <v>1.0381235801548705E-17</v>
       </c>
     </row>
@@ -2081,7 +2089,7 @@
       <c r="I42" t="str">
         <v>Commodity ETF</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="7">
         <v>1.3877787807814457E-17</v>
       </c>
     </row>
@@ -2107,6 +2115,7 @@
       <c r="G43" s="1">
         <v>-2.2479658556640549E-2</v>
       </c>
+      <c r="J43" s="7"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="5">
@@ -2130,6 +2139,7 @@
       <c r="G44" s="1">
         <v>8.7755777822764502E-2</v>
       </c>
+      <c r="J44" s="7"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="5">
@@ -2157,7 +2167,7 @@
         <f t="array" ref="I45:J47">_xlfn._xlws.PY(7,0)</f>
         <v>Metric</v>
       </c>
-      <c r="J45" t="str">
+      <c r="J45" s="7" t="str">
         <v>Value</v>
       </c>
     </row>
@@ -2186,7 +2196,7 @@
       <c r="I46" t="str">
         <v>Expected Monthly Return</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="7">
         <v>6.1915890479674685E-3</v>
       </c>
     </row>
@@ -2215,7 +2225,7 @@
       <c r="I47" t="str">
         <v>Monthly Risk</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="7">
         <v>9.2664601849919061E-3</v>
       </c>
     </row>
